--- a/output/2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore macchine per lavorazione legno e metallo, utensili professionali. Sede legale Starše, punto vendita Maribor.</t>
+          <t>Distributore macchine per lavorazione legno e metallo, utensili professionali. Sede legale Starše, punto vendita Maribor. [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vendita, assistenza e installazione macchine per lavorazione legno/metallo, utensili elettrici professionali (Holzmann, Sicar, Robland, Zipper, Virutex).</t>
+          <t>Vendita, assistenza e installazione macchine per lavorazione legno/metallo, utensili elettrici professionali (Holzmann, Sicar, Robland, Zipper, Virutex). [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore macchine CNC e attrezzature per lavorazione metalli, utensili da taglio. Attiva dal 1992.</t>
+          <t>Distributore macchine CNC e attrezzature per lavorazione metalli, utensili da taglio. Attiva dal 1992. [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sistemi di aspirazione/filtrazione industriale per polveri, fumi, nebbia oleosa.</t>
+          <t>Sistemi di aspirazione/filtrazione industriale per polveri, fumi, nebbia oleosa. [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
